--- a/matlab/results/statistical_summary.xlsx
+++ b/matlab/results/statistical_summary.xlsx
@@ -22,22 +22,22 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>Sehir</t>
-  </si>
-  <si>
-    <t>Bolge</t>
-  </si>
-  <si>
-    <t>Urun</t>
-  </si>
-  <si>
-    <t>Kategori</t>
-  </si>
-  <si>
-    <t>Satis_Kanali</t>
-  </si>
-  <si>
-    <t>Musteri_Tipi</t>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Sales_Channel</t>
+  </si>
+  <si>
+    <t>Customer_Type</t>
   </si>
   <si>
     <t>Number_of_Groups</t>
@@ -97,19 +97,19 @@
     <t>Adana vs Ankara</t>
   </si>
   <si>
-    <t>Karadeniz vs Güneydoğu Anadolu</t>
+    <t>Black Sea vs Southeastern Anatolia</t>
   </si>
   <si>
     <t>Office Chair vs Pen Set</t>
   </si>
   <si>
-    <t>Mobilya vs Kırtasiye</t>
-  </si>
-  <si>
-    <t>Mağaza vs Bayi</t>
-  </si>
-  <si>
-    <t>Kurumsal vs Bireysel</t>
+    <t>Furniture vs Stationery</t>
+  </si>
+  <si>
+    <t>Store vs Dealer</t>
+  </si>
+  <si>
+    <t>Corporate vs Individual</t>
   </si>
   <si>
     <t>ANOVA_perm_agree</t>
@@ -145,6 +145,12 @@
     <t>Gaziantep</t>
   </si>
   <si>
+    <t>Istanbul</t>
+  </si>
+  <si>
+    <t>Izmir</t>
+  </si>
+  <si>
     <t>Konya</t>
   </si>
   <si>
@@ -154,28 +160,22 @@
     <t>Trabzon</t>
   </si>
   <si>
-    <t>İstanbul</t>
-  </si>
-  <si>
-    <t>İzmir</t>
-  </si>
-  <si>
-    <t>Akdeniz</t>
-  </si>
-  <si>
-    <t>Ege</t>
-  </si>
-  <si>
-    <t>Güneydoğu Anadolu</t>
-  </si>
-  <si>
-    <t>Karadeniz</t>
+    <t>Aegean</t>
+  </si>
+  <si>
+    <t>Black Sea</t>
+  </si>
+  <si>
+    <t>Central Anatolia</t>
   </si>
   <si>
     <t>Marmara</t>
   </si>
   <si>
-    <t>İç Anadolu</t>
+    <t>Mediterranean</t>
+  </si>
+  <si>
+    <t>Southeastern Anatolia</t>
   </si>
   <si>
     <t>Backpack</t>
@@ -214,37 +214,37 @@
     <t>Wireless Mouse</t>
   </si>
   <si>
-    <t>Aksesuar</t>
-  </si>
-  <si>
-    <t>Elektronik</t>
-  </si>
-  <si>
-    <t>Kırtasiye</t>
-  </si>
-  <si>
-    <t>Mobilya</t>
-  </si>
-  <si>
-    <t>Ofis Aksesuarları</t>
-  </si>
-  <si>
-    <t>Bayi</t>
-  </si>
-  <si>
-    <t>Mağaza</t>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Office Accessories</t>
+  </si>
+  <si>
+    <t>Stationery</t>
+  </si>
+  <si>
+    <t>Dealer</t>
   </si>
   <si>
     <t>Online</t>
   </si>
   <si>
-    <t>Bireysel</t>
-  </si>
-  <si>
-    <t>KOBI</t>
-  </si>
-  <si>
-    <t>Kurumsal</t>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>SME</t>
   </si>
   <si>
     <t>TestPrimary</t>
@@ -338,7 +338,7 @@
   <dimension ref="A1:W7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14" customWidth="true"/>
     <col min="2" max="2" width="18.5703125" customWidth="true"/>
     <col min="3" max="3" width="4.140625" customWidth="true"/>
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
@@ -356,7 +356,7 @@
     <col min="16" max="16" width="18" customWidth="true"/>
     <col min="17" max="17" width="16.140625" customWidth="true"/>
     <col min="18" max="18" width="17.7109375" customWidth="true"/>
-    <col min="19" max="19" width="30.5703125" customWidth="true"/>
+    <col min="19" max="19" width="31.7109375" customWidth="true"/>
     <col min="20" max="20" width="19.5703125" customWidth="true"/>
     <col min="21" max="21" width="20.5703125" customWidth="true"/>
     <col min="22" max="22" width="15.5703125" customWidth="true"/>
@@ -445,10 +445,10 @@
         <v>958</v>
       </c>
       <c r="D2" s="0">
-        <v>1.1434475864354774</v>
+        <v>1.1434475864354776</v>
       </c>
       <c r="E2" s="0">
-        <v>0.32881725277119056</v>
+        <v>0.32881725277118989</v>
       </c>
       <c r="F2" s="0">
         <v>0.32326767323267674</v>
@@ -457,10 +457,10 @@
         <v>0.41917059047051575</v>
       </c>
       <c r="H2" s="0">
-        <v>0.010738938354053691</v>
+        <v>0.010738938354053693</v>
       </c>
       <c r="I2" s="0">
-        <v>0.0013458150236606505</v>
+        <v>0.0013458150236606524</v>
       </c>
       <c r="J2" s="0">
         <v>0.32326767323267674</v>
@@ -481,7 +481,7 @@
         <v>9.1983436450515583</v>
       </c>
       <c r="P2" s="0">
-        <v>1.0005427248586463</v>
+        <v>1.000542724858646</v>
       </c>
       <c r="Q2" s="0">
         <v>1.8909327544574053</v>
@@ -499,7 +499,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="0">
-        <v>0.32881725277119056</v>
+        <v>0.32881725277118989</v>
       </c>
       <c r="W2" s="0" t="b">
         <v>0</v>
@@ -516,10 +516,10 @@
         <v>958</v>
       </c>
       <c r="D3" s="0">
-        <v>1.3887377596759973</v>
+        <v>1.3887377596759971</v>
       </c>
       <c r="E3" s="0">
-        <v>0.22594591349983451</v>
+        <v>0.22594591349983417</v>
       </c>
       <c r="F3" s="0">
         <v>0.22037796220377962</v>
@@ -528,10 +528,10 @@
         <v>0.35201503648091148</v>
       </c>
       <c r="H3" s="0">
-        <v>0.0072409765865197873</v>
+        <v>0.0072409765865197864</v>
       </c>
       <c r="I3" s="0">
-        <v>0.0020247946010385478</v>
+        <v>0.0020247946010385465</v>
       </c>
       <c r="J3" s="0">
         <v>0.26445355464453557</v>
@@ -555,7 +555,7 @@
         <v>0.99829672858558949</v>
       </c>
       <c r="Q3" s="0">
-        <v>2.220972474940591</v>
+        <v>2.2209724749405915</v>
       </c>
       <c r="R3" s="0">
         <v>578.07681159420281</v>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="0">
-        <v>0.27113509619980142</v>
+        <v>0.27113509619980103</v>
       </c>
       <c r="W3" s="0" t="b">
         <v>0</v>
@@ -697,7 +697,7 @@
         <v>1.0062342050407269</v>
       </c>
       <c r="Q5" s="0">
-        <v>2.3956115036467041</v>
+        <v>2.3956115036467045</v>
       </c>
       <c r="R5" s="0">
         <v>3707.9844791965566</v>
@@ -830,13 +830,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="0">
-        <v>0.00084373312974620124</v>
+        <v>0.00084373312974620428</v>
       </c>
       <c r="O7" s="0">
         <v>22.379310528986984</v>
       </c>
       <c r="P7" s="0">
-        <v>0.98391604277043476</v>
+        <v>0.98391604277043498</v>
       </c>
       <c r="Q7" s="0">
         <v>2.916054832197343</v>
@@ -870,14 +870,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="true"/>
-    <col min="2" max="2" width="12.28515625" customWidth="true"/>
+    <col min="2" max="2" width="15" customWidth="true"/>
     <col min="3" max="3" width="14.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.42578125" customWidth="true"/>
     <col min="5" max="5" width="15.5703125" customWidth="true"/>
     <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="15.7109375" customWidth="true"/>
     <col min="8" max="8" width="17.7109375" customWidth="true"/>
-    <col min="9" max="9" width="30.5703125" customWidth="true"/>
+    <col min="9" max="9" width="31.7109375" customWidth="true"/>
     <col min="10" max="10" width="19.5703125" customWidth="true"/>
     <col min="11" max="11" width="10.42578125" customWidth="true"/>
   </cols>
@@ -1071,13 +1071,13 @@
         <v>0.22037796220377962</v>
       </c>
       <c r="E6" s="0">
-        <v>0.22594591349983451</v>
+        <v>0.22594591349983417</v>
       </c>
       <c r="F6" s="0">
-        <v>0.0072409765865197873</v>
+        <v>0.0072409765865197864</v>
       </c>
       <c r="G6" s="0">
-        <v>0.0020247946010385478</v>
+        <v>0.0020247946010385465</v>
       </c>
       <c r="H6" s="0">
         <v>578.07681159420281</v>
@@ -1106,13 +1106,13 @@
         <v>0.32326767323267674</v>
       </c>
       <c r="E7" s="0">
-        <v>0.32881725277119056</v>
+        <v>0.32881725277118989</v>
       </c>
       <c r="F7" s="0">
-        <v>0.010738938354053691</v>
+        <v>0.010738938354053693</v>
       </c>
       <c r="G7" s="0">
-        <v>0.0013458150236606505</v>
+        <v>0.0013458150236606524</v>
       </c>
       <c r="H7" s="0">
         <v>726.03546103395024</v>
@@ -1136,8 +1136,8 @@
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="true"/>
-    <col min="2" max="2" width="20" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
+    <col min="2" max="2" width="20.85546875" customWidth="true"/>
     <col min="3" max="3" width="4.140625" customWidth="true"/>
     <col min="4" max="4" width="16.7109375" customWidth="true"/>
     <col min="5" max="5" width="9.140625" customWidth="true"/>
@@ -1348,7 +1348,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="0">
-        <v>59</v>
+        <v>291</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>77</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1380,7 @@
         <v>43</v>
       </c>
       <c r="C8" s="0">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>77</v>
@@ -1412,7 +1412,7 @@
         <v>44</v>
       </c>
       <c r="C9" s="0">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>77</v>
@@ -1444,7 +1444,7 @@
         <v>45</v>
       </c>
       <c r="C10" s="0">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>77</v>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -1476,7 +1476,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="0">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>77</v>
@@ -1508,7 +1508,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="0">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>77</v>
@@ -1540,7 +1540,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="0">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>77</v>
@@ -1572,7 +1572,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="0">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>77</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15">
@@ -1604,7 +1604,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="0">
-        <v>69</v>
+        <v>378</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>77</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -1636,7 +1636,7 @@
         <v>51</v>
       </c>
       <c r="C16" s="0">
-        <v>378</v>
+        <v>125</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>77</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -1668,7 +1668,7 @@
         <v>52</v>
       </c>
       <c r="C17" s="0">
-        <v>221</v>
+        <v>46</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>77</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -2148,7 +2148,7 @@
         <v>67</v>
       </c>
       <c r="C32" s="0">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>77</v>
@@ -2163,7 +2163,7 @@
         <v>0.00050000000000000001</v>
       </c>
       <c r="H32" s="0">
-        <v>0.001</v>
+        <v>0.0036099507796000414</v>
       </c>
       <c r="I32" s="0" t="b">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>68</v>
       </c>
       <c r="C33" s="0">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>77</v>
@@ -2195,7 +2195,7 @@
         <v>0.00050000000000000001</v>
       </c>
       <c r="H33" s="0">
-        <v>0.0036099507796000414</v>
+        <v>0.001</v>
       </c>
       <c r="I33" s="0" t="b">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>77</v>
@@ -2276,7 +2276,7 @@
         <v>71</v>
       </c>
       <c r="C36" s="0">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>77</v>
@@ -2308,7 +2308,7 @@
         <v>72</v>
       </c>
       <c r="C37" s="0">
-        <v>494</v>
+        <v>334</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>77</v>
@@ -2340,7 +2340,7 @@
         <v>73</v>
       </c>
       <c r="C38" s="0">
-        <v>527</v>
+        <v>162</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>77</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
@@ -2372,7 +2372,7 @@
         <v>74</v>
       </c>
       <c r="C39" s="0">
-        <v>269</v>
+        <v>527</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>77</v>
@@ -2404,7 +2404,7 @@
         <v>75</v>
       </c>
       <c r="C40" s="0">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>77</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2437,8 +2437,8 @@
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="true"/>
-    <col min="2" max="2" width="20" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
+    <col min="2" max="2" width="20.85546875" customWidth="true"/>
     <col min="3" max="3" width="4.140625" customWidth="true"/>
     <col min="4" max="4" width="6.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.7109375" customWidth="true"/>
@@ -2592,19 +2592,19 @@
         <v>42</v>
       </c>
       <c r="C7" s="0">
-        <v>59</v>
+        <v>291</v>
       </c>
       <c r="D7" s="0">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E7" s="0">
-        <v>6.7796610169491522</v>
+        <v>8.2474226804123703</v>
       </c>
       <c r="F7" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G7" s="0">
-        <v>1.6949152542372881</v>
+        <v>2.7491408934707904</v>
       </c>
     </row>
     <row r="8">
@@ -2615,19 +2615,19 @@
         <v>43</v>
       </c>
       <c r="C8" s="0">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="D8" s="0">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="0">
-        <v>12.820512820512821</v>
+        <v>6.7226890756302522</v>
       </c>
       <c r="F8" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" s="0">
-        <v>2.5641025641025643</v>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="9">
@@ -2638,19 +2638,19 @@
         <v>44</v>
       </c>
       <c r="C9" s="0">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D9" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="0">
-        <v>6.666666666666667</v>
+        <v>6.7796610169491522</v>
       </c>
       <c r="F9" s="0">
         <v>1</v>
       </c>
       <c r="G9" s="0">
-        <v>3.3333333333333335</v>
+        <v>1.6949152542372881</v>
       </c>
     </row>
     <row r="10">
@@ -2661,19 +2661,19 @@
         <v>45</v>
       </c>
       <c r="C10" s="0">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="D10" s="0">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E10" s="0">
-        <v>8.2474226804123703</v>
+        <v>12.820512820512821</v>
       </c>
       <c r="F10" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G10" s="0">
-        <v>2.7491408934707904</v>
+        <v>2.5641025641025643</v>
       </c>
     </row>
     <row r="11">
@@ -2684,19 +2684,19 @@
         <v>46</v>
       </c>
       <c r="C11" s="0">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="D11" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E11" s="0">
-        <v>6.7226890756302522</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F11" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="0">
-        <v>3.3613445378151261</v>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="12">
@@ -2707,19 +2707,19 @@
         <v>47</v>
       </c>
       <c r="C12" s="0">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D12" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="0">
-        <v>9.5999999999999997</v>
+        <v>6.7226890756302522</v>
       </c>
       <c r="F12" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" s="0">
-        <v>1.6000000000000001</v>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="13">
@@ -2730,19 +2730,19 @@
         <v>48</v>
       </c>
       <c r="C13" s="0">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D13" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E13" s="0">
-        <v>6.7226890756302522</v>
+        <v>14.492753623188406</v>
       </c>
       <c r="F13" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="0">
-        <v>3.3613445378151261</v>
+        <v>2.8985507246376812</v>
       </c>
     </row>
     <row r="14">
@@ -2753,19 +2753,19 @@
         <v>49</v>
       </c>
       <c r="C14" s="0">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="D14" s="0">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E14" s="0">
-        <v>10.869565217391305</v>
+        <v>7.6923076923076925</v>
       </c>
       <c r="F14" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G14" s="0">
-        <v>2.1739130434782608</v>
+        <v>2.7149321266968327</v>
       </c>
     </row>
     <row r="15">
@@ -2776,19 +2776,19 @@
         <v>50</v>
       </c>
       <c r="C15" s="0">
-        <v>69</v>
+        <v>378</v>
       </c>
       <c r="D15" s="0">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E15" s="0">
-        <v>14.492753623188406</v>
+        <v>8.4656084656084651</v>
       </c>
       <c r="F15" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G15" s="0">
-        <v>2.8985507246376812</v>
+        <v>2.3809523809523809</v>
       </c>
     </row>
     <row r="16">
@@ -2799,19 +2799,19 @@
         <v>51</v>
       </c>
       <c r="C16" s="0">
-        <v>378</v>
+        <v>125</v>
       </c>
       <c r="D16" s="0">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E16" s="0">
-        <v>8.4656084656084651</v>
+        <v>9.5999999999999997</v>
       </c>
       <c r="F16" s="0">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G16" s="0">
-        <v>2.3809523809523809</v>
+        <v>1.6000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2822,19 +2822,19 @@
         <v>52</v>
       </c>
       <c r="C17" s="0">
-        <v>221</v>
+        <v>46</v>
       </c>
       <c r="D17" s="0">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E17" s="0">
-        <v>7.6923076923076925</v>
+        <v>10.869565217391305</v>
       </c>
       <c r="F17" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G17" s="0">
-        <v>2.7149321266968327</v>
+        <v>2.1739130434782608</v>
       </c>
     </row>
     <row r="18">
@@ -3167,19 +3167,19 @@
         <v>67</v>
       </c>
       <c r="C32" s="0">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="D32" s="0">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E32" s="0">
-        <v>6.7073170731707315</v>
+        <v>4.7058823529411766</v>
       </c>
       <c r="F32" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32" s="0">
-        <v>2.4390243902439024</v>
+        <v>1.1764705882352942</v>
       </c>
     </row>
     <row r="33">
@@ -3190,19 +3190,19 @@
         <v>68</v>
       </c>
       <c r="C33" s="0">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D33" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33" s="0">
-        <v>4.7058823529411766</v>
+        <v>4.375</v>
       </c>
       <c r="F33" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="0">
-        <v>1.1764705882352942</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="34">
@@ -3213,19 +3213,19 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D34" s="0">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E34" s="0">
-        <v>4.375</v>
+        <v>6.7073170731707315</v>
       </c>
       <c r="F34" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" s="0">
-        <v>1.25</v>
+        <v>2.4390243902439024</v>
       </c>
     </row>
     <row r="35">
@@ -3259,19 +3259,19 @@
         <v>71</v>
       </c>
       <c r="C36" s="0">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="D36" s="0">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E36" s="0">
-        <v>10.479041916167665</v>
+        <v>8.5020242914979764</v>
       </c>
       <c r="F36" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G36" s="0">
-        <v>3.2934131736526946</v>
+        <v>2.0242914979757085</v>
       </c>
     </row>
     <row r="37">
@@ -3282,19 +3282,19 @@
         <v>72</v>
       </c>
       <c r="C37" s="0">
-        <v>494</v>
+        <v>334</v>
       </c>
       <c r="D37" s="0">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E37" s="0">
-        <v>8.5020242914979764</v>
+        <v>10.479041916167665</v>
       </c>
       <c r="F37" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="0">
-        <v>2.0242914979757085</v>
+        <v>3.2934131736526946</v>
       </c>
     </row>
     <row r="38">
@@ -3305,19 +3305,19 @@
         <v>73</v>
       </c>
       <c r="C38" s="0">
-        <v>527</v>
+        <v>162</v>
       </c>
       <c r="D38" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E38" s="0">
-        <v>8.5388994307400381</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="F38" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G38" s="0">
-        <v>2.0872865275142316</v>
+        <v>1.8518518518518519</v>
       </c>
     </row>
     <row r="39">
@@ -3328,19 +3328,19 @@
         <v>74</v>
       </c>
       <c r="C39" s="0">
-        <v>269</v>
+        <v>527</v>
       </c>
       <c r="D39" s="0">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E39" s="0">
-        <v>10.408921933085502</v>
+        <v>8.5388994307400381</v>
       </c>
       <c r="F39" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G39" s="0">
-        <v>2.2304832713754648</v>
+        <v>2.0872865275142316</v>
       </c>
     </row>
     <row r="40">
@@ -3351,19 +3351,19 @@
         <v>75</v>
       </c>
       <c r="C40" s="0">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="D40" s="0">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E40" s="0">
-        <v>11.111111111111111</v>
+        <v>10.408921933085502</v>
       </c>
       <c r="F40" s="0">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G40" s="0">
-        <v>1.8518518518518519</v>
+        <v>2.2304832713754648</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3375,7 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14" customWidth="true"/>
     <col min="2" max="2" width="15.5703125" customWidth="true"/>
     <col min="3" max="3" width="15.5703125" customWidth="true"/>
     <col min="4" max="4" width="14.42578125" customWidth="true"/>
@@ -3403,7 +3403,7 @@
         <v>0.023678478592389609</v>
       </c>
       <c r="C2" s="0">
-        <v>0.32881725277119056</v>
+        <v>0.32881725277118989</v>
       </c>
       <c r="D2" s="0">
         <v>0.32326767323267674</v>
@@ -3417,7 +3417,7 @@
         <v>0.07142915475015002</v>
       </c>
       <c r="C3" s="0">
-        <v>0.22594591349983451</v>
+        <v>0.22594591349983417</v>
       </c>
       <c r="D3" s="0">
         <v>0.22037796220377962</v>
@@ -3470,7 +3470,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>0.00084373312974620124</v>
+        <v>0.00084373312974620428</v>
       </c>
       <c r="C7" s="0">
         <v>5.3893376947754505e-05</v>
